--- a/demo/samples/bearings/03-outstanding.xlsx
+++ b/demo/samples/bearings/03-outstanding.xlsx
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46207</v>
+        <v>46212</v>
       </c>
       <c r="E6" t="n">
         <v>58800</v>
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46215</v>
+        <v>46220</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="E7" t="n">
         <v>39000</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="E8" t="n">
         <v>14400</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="E9" t="n">
         <v>21300</v>
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="E10" t="n">
         <v>46500</v>

--- a/demo/samples/bearings/03-outstanding.xlsx
+++ b/demo/samples/bearings/03-outstanding.xlsx
@@ -430,7 +430,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -479,7 +479,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Outstanding Amount</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
